--- a/Reference_seqs/HCV_Subtype_Ref_vs_Comet_Subtype_Consensus_Aligned_NS5A_NTD.xlsx
+++ b/Reference_seqs/HCV_Subtype_Ref_vs_Comet_Subtype_Consensus_Aligned_NS5A_NTD.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P380"/>
+  <dimension ref="A1:P384"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -17075,11 +17075,7 @@
       <c r="F376" t="inlineStr"/>
       <c r="G376" t="inlineStr"/>
       <c r="H376" t="inlineStr"/>
-      <c r="I376" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="I376" t="inlineStr"/>
       <c r="J376" t="inlineStr"/>
       <c r="K376" t="inlineStr"/>
       <c r="L376" t="inlineStr"/>
@@ -17155,12 +17151,12 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>GT8</t>
+          <t>GT7</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>8a</t>
+          <t>7b</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
@@ -17175,7 +17171,7 @@
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>K</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
@@ -17215,17 +17211,17 @@
       </c>
       <c r="N379" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>N</t>
         </is>
       </c>
       <c r="O379" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="P379" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>H</t>
         </is>
       </c>
     </row>
@@ -17237,12 +17233,12 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>GT8</t>
+          <t>GT7</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>8a</t>
+          <t>7b</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
@@ -17251,25 +17247,204 @@
         </is>
       </c>
       <c r="E380" t="inlineStr"/>
-      <c r="F380" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
+      <c r="F380" t="inlineStr"/>
       <c r="G380" t="inlineStr"/>
       <c r="H380" t="inlineStr"/>
-      <c r="I380" t="inlineStr"/>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="J380" t="inlineStr"/>
       <c r="K380" t="inlineStr"/>
       <c r="L380" t="inlineStr"/>
       <c r="M380" t="inlineStr"/>
-      <c r="N380" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+      <c r="N380" t="inlineStr"/>
       <c r="O380" t="inlineStr"/>
       <c r="P380" t="inlineStr"/>
+    </row>
+    <row r="381"/>
+    <row r="382">
+      <c r="A382" s="1" t="inlineStr">
+        <is>
+          <t>Gene</t>
+        </is>
+      </c>
+      <c r="B382" s="1" t="inlineStr">
+        <is>
+          <t>Genotype</t>
+        </is>
+      </c>
+      <c r="C382" s="1" t="inlineStr">
+        <is>
+          <t>Subtype</t>
+        </is>
+      </c>
+      <c r="D382" s="1" t="inlineStr">
+        <is>
+          <t>Sequence</t>
+        </is>
+      </c>
+      <c r="E382" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="F382" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="G382" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="H382" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="I382" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="J382" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="K382" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="L382" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="M382" s="1" t="n">
+        <v>58</v>
+      </c>
+      <c r="N382" s="1" t="n">
+        <v>62</v>
+      </c>
+      <c r="O382" s="1" t="n">
+        <v>92</v>
+      </c>
+      <c r="P382" s="1" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>NS5A_NTD</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>GT8</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>8a</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="J383" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="M383" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="N383" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="O383" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="P383" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>NS5A_NTD</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>GT8</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>8a</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>Consensus</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr"/>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr"/>
+      <c r="H384" t="inlineStr"/>
+      <c r="I384" t="inlineStr"/>
+      <c r="J384" t="inlineStr"/>
+      <c r="K384" t="inlineStr"/>
+      <c r="L384" t="inlineStr"/>
+      <c r="M384" t="inlineStr"/>
+      <c r="N384" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="O384" t="inlineStr"/>
+      <c r="P384" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Reference_seqs/HCV_Subtype_Ref_vs_Comet_Subtype_Consensus_Aligned_NS5A_NTD.xlsx
+++ b/Reference_seqs/HCV_Subtype_Ref_vs_Comet_Subtype_Consensus_Aligned_NS5A_NTD.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P384"/>
+  <dimension ref="A1:P380"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1305,7 +1305,11 @@
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
@@ -15736,7 +15740,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>6u</t>
+          <t>6v</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -15746,57 +15750,57 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>V</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>S</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>P</t>
         </is>
       </c>
       <c r="J347" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>G</t>
         </is>
       </c>
       <c r="K347" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>I</t>
         </is>
       </c>
       <c r="L347" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>G</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>T</t>
         </is>
       </c>
       <c r="O347" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>T</t>
         </is>
       </c>
       <c r="P347" t="inlineStr">
@@ -15818,7 +15822,7 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>6u</t>
+          <t>6v</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -15951,7 +15955,7 @@
       </c>
       <c r="K351" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>V</t>
         </is>
       </c>
       <c r="L351" t="inlineStr">
@@ -16007,7 +16011,11 @@
       <c r="H352" t="inlineStr"/>
       <c r="I352" t="inlineStr"/>
       <c r="J352" t="inlineStr"/>
-      <c r="K352" t="inlineStr"/>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="L352" t="inlineStr"/>
       <c r="M352" t="inlineStr"/>
       <c r="N352" t="inlineStr"/>
@@ -16086,7 +16094,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>6v</t>
+          <t>6w</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -16096,17 +16104,17 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>K</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>F</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
@@ -16126,7 +16134,7 @@
       </c>
       <c r="K355" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>I</t>
         </is>
       </c>
       <c r="L355" t="inlineStr">
@@ -16141,7 +16149,7 @@
       </c>
       <c r="N355" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>A</t>
         </is>
       </c>
       <c r="O355" t="inlineStr">
@@ -16168,7 +16176,7 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>6v</t>
+          <t>6w</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -16177,19 +16185,23 @@
         </is>
       </c>
       <c r="E356" t="inlineStr"/>
-      <c r="F356" t="inlineStr"/>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="G356" t="inlineStr"/>
       <c r="H356" t="inlineStr"/>
       <c r="I356" t="inlineStr"/>
       <c r="J356" t="inlineStr"/>
-      <c r="K356" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+      <c r="K356" t="inlineStr"/>
       <c r="L356" t="inlineStr"/>
       <c r="M356" t="inlineStr"/>
-      <c r="N356" t="inlineStr"/>
+      <c r="N356" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
       <c r="O356" t="inlineStr"/>
       <c r="P356" t="inlineStr"/>
     </row>
@@ -16448,7 +16460,7 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>6w</t>
+          <t>6xa</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -16463,12 +16475,12 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>V</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
@@ -16488,7 +16500,7 @@
       </c>
       <c r="K363" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>V</t>
         </is>
       </c>
       <c r="L363" t="inlineStr">
@@ -16503,7 +16515,7 @@
       </c>
       <c r="N363" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>T</t>
         </is>
       </c>
       <c r="O363" t="inlineStr">
@@ -16530,7 +16542,7 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>6w</t>
+          <t>6xa</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -16539,11 +16551,7 @@
         </is>
       </c>
       <c r="E364" t="inlineStr"/>
-      <c r="F364" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
+      <c r="F364" t="inlineStr"/>
       <c r="G364" t="inlineStr"/>
       <c r="H364" t="inlineStr"/>
       <c r="I364" t="inlineStr"/>
@@ -16551,11 +16559,7 @@
       <c r="K364" t="inlineStr"/>
       <c r="L364" t="inlineStr"/>
       <c r="M364" t="inlineStr"/>
-      <c r="N364" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
+      <c r="N364" t="inlineStr"/>
       <c r="O364" t="inlineStr"/>
       <c r="P364" t="inlineStr"/>
     </row>
@@ -16801,12 +16805,12 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>GT6</t>
+          <t>GT7</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>6xa</t>
+          <t>7a</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
@@ -16821,57 +16825,57 @@
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>K</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
         <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
           <t>S</t>
         </is>
       </c>
-      <c r="H371" t="inlineStr">
+      <c r="J371" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I371" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="J371" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
       <c r="K371" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>P</t>
         </is>
       </c>
       <c r="L371" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>S</t>
         </is>
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>P</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>L</t>
         </is>
       </c>
       <c r="O371" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>S</t>
         </is>
       </c>
       <c r="P371" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>H</t>
         </is>
       </c>
     </row>
@@ -16883,12 +16887,12 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>GT6</t>
+          <t>GT7</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>6xa</t>
+          <t>7a</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
@@ -16981,7 +16985,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>7a</t>
+          <t>7b</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
@@ -17036,12 +17040,12 @@
       </c>
       <c r="N375" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>N</t>
         </is>
       </c>
       <c r="O375" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="P375" t="inlineStr">
@@ -17063,7 +17067,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>7a</t>
+          <t>7b</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
@@ -17075,7 +17079,11 @@
       <c r="F376" t="inlineStr"/>
       <c r="G376" t="inlineStr"/>
       <c r="H376" t="inlineStr"/>
-      <c r="I376" t="inlineStr"/>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="J376" t="inlineStr"/>
       <c r="K376" t="inlineStr"/>
       <c r="L376" t="inlineStr"/>
@@ -17151,12 +17159,12 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>GT7</t>
+          <t>GT8</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>7b</t>
+          <t>8a</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
@@ -17171,7 +17179,7 @@
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>R</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
@@ -17211,17 +17219,17 @@
       </c>
       <c r="N379" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>V</t>
         </is>
       </c>
       <c r="O379" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="P379" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>S</t>
         </is>
       </c>
     </row>
@@ -17233,12 +17241,12 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>GT7</t>
+          <t>GT8</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>7b</t>
+          <t>8a</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
@@ -17247,204 +17255,25 @@
         </is>
       </c>
       <c r="E380" t="inlineStr"/>
-      <c r="F380" t="inlineStr"/>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
       <c r="G380" t="inlineStr"/>
       <c r="H380" t="inlineStr"/>
-      <c r="I380" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
+      <c r="I380" t="inlineStr"/>
       <c r="J380" t="inlineStr"/>
       <c r="K380" t="inlineStr"/>
       <c r="L380" t="inlineStr"/>
       <c r="M380" t="inlineStr"/>
-      <c r="N380" t="inlineStr"/>
+      <c r="N380" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="O380" t="inlineStr"/>
       <c r="P380" t="inlineStr"/>
-    </row>
-    <row r="381"/>
-    <row r="382">
-      <c r="A382" s="1" t="inlineStr">
-        <is>
-          <t>Gene</t>
-        </is>
-      </c>
-      <c r="B382" s="1" t="inlineStr">
-        <is>
-          <t>Genotype</t>
-        </is>
-      </c>
-      <c r="C382" s="1" t="inlineStr">
-        <is>
-          <t>Subtype</t>
-        </is>
-      </c>
-      <c r="D382" s="1" t="inlineStr">
-        <is>
-          <t>Sequence</t>
-        </is>
-      </c>
-      <c r="E382" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="F382" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="G382" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="H382" s="1" t="n">
-        <v>29</v>
-      </c>
-      <c r="I382" s="1" t="n">
-        <v>30</v>
-      </c>
-      <c r="J382" s="1" t="n">
-        <v>31</v>
-      </c>
-      <c r="K382" s="1" t="n">
-        <v>32</v>
-      </c>
-      <c r="L382" s="1" t="n">
-        <v>38</v>
-      </c>
-      <c r="M382" s="1" t="n">
-        <v>58</v>
-      </c>
-      <c r="N382" s="1" t="n">
-        <v>62</v>
-      </c>
-      <c r="O382" s="1" t="n">
-        <v>92</v>
-      </c>
-      <c r="P382" s="1" t="n">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="383">
-      <c r="A383" t="inlineStr">
-        <is>
-          <t>NS5A_NTD</t>
-        </is>
-      </c>
-      <c r="B383" t="inlineStr">
-        <is>
-          <t>GT8</t>
-        </is>
-      </c>
-      <c r="C383" t="inlineStr">
-        <is>
-          <t>8a</t>
-        </is>
-      </c>
-      <c r="D383" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="E383" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="F383" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="G383" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="H383" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="I383" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="J383" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="K383" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="L383" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="M383" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="N383" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="O383" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="P383" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-    </row>
-    <row r="384">
-      <c r="A384" t="inlineStr">
-        <is>
-          <t>NS5A_NTD</t>
-        </is>
-      </c>
-      <c r="B384" t="inlineStr">
-        <is>
-          <t>GT8</t>
-        </is>
-      </c>
-      <c r="C384" t="inlineStr">
-        <is>
-          <t>8a</t>
-        </is>
-      </c>
-      <c r="D384" t="inlineStr">
-        <is>
-          <t>Consensus</t>
-        </is>
-      </c>
-      <c r="E384" t="inlineStr"/>
-      <c r="F384" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="G384" t="inlineStr"/>
-      <c r="H384" t="inlineStr"/>
-      <c r="I384" t="inlineStr"/>
-      <c r="J384" t="inlineStr"/>
-      <c r="K384" t="inlineStr"/>
-      <c r="L384" t="inlineStr"/>
-      <c r="M384" t="inlineStr"/>
-      <c r="N384" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="O384" t="inlineStr"/>
-      <c r="P384" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Reference_seqs/HCV_Subtype_Ref_vs_Comet_Subtype_Consensus_Aligned_NS5A_NTD.xlsx
+++ b/Reference_seqs/HCV_Subtype_Ref_vs_Comet_Subtype_Consensus_Aligned_NS5A_NTD.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P380"/>
+  <dimension ref="A1:Q380"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -436,6 +436,7 @@
     <col width="4" customWidth="1" min="14" max="14"/>
     <col width="4" customWidth="1" min="15" max="15"/>
     <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="50" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -496,6 +497,11 @@
       <c r="P2" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q2" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -600,18 +606,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5"/>
     <row r="6">
@@ -671,6 +665,11 @@
       <c r="P6" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q6" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -775,18 +774,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9"/>
     <row r="10">
@@ -846,6 +833,11 @@
       <c r="P10" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q10" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -950,18 +942,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13"/>
     <row r="14">
@@ -1021,6 +1001,11 @@
       <c r="P14" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q14" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1125,22 +1110,24 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <r>
+            <t>Q30R</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>93</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="17"/>
     <row r="18">
@@ -1200,6 +1187,11 @@
       <c r="P18" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q18" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1304,22 +1296,24 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <r>
+            <t>V26M</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>NA</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="21"/>
     <row r="22">
@@ -1379,6 +1373,11 @@
       <c r="P22" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q22" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1483,22 +1482,24 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <r>
+            <t>H92Y</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>NA</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="25"/>
     <row r="26">
@@ -1558,6 +1559,11 @@
       <c r="P26" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q26" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1662,22 +1668,24 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <r>
+            <t>R30L</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>33</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="29"/>
     <row r="30">
@@ -1737,6 +1745,11 @@
       <c r="P30" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q30" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1846,21 +1859,36 @@
           <t>R</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <r>
+            <t>K24R</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>57</t>
+          </r>
+          <r>
+            <t xml:space="preserve">, </t>
+          </r>
+          <r>
+            <t>S58P</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>86</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="33"/>
     <row r="34">
@@ -1920,6 +1948,11 @@
       <c r="P34" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q34" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2024,22 +2057,24 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <r>
+            <t>L31M</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>57</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="37"/>
     <row r="38">
@@ -2099,6 +2134,11 @@
       <c r="P38" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q38" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2208,21 +2248,36 @@
           <t>R</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>Q</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <r>
+            <t>S24R</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>80</t>
+          </r>
+          <r>
+            <t xml:space="preserve">, </t>
+          </r>
+          <r>
+            <t>R30Q</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>75</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="41"/>
     <row r="42">
@@ -2282,6 +2337,11 @@
       <c r="P42" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q42" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2386,18 +2446,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
     </row>
     <row r="45"/>
     <row r="46">
@@ -2457,6 +2505,11 @@
       <c r="P46" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q46" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2561,18 +2614,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
     </row>
     <row r="49"/>
     <row r="50">
@@ -2632,6 +2673,11 @@
       <c r="P50" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q50" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2736,18 +2782,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
     </row>
     <row r="53"/>
     <row r="54">
@@ -2807,6 +2841,11 @@
       <c r="P54" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q54" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2911,22 +2950,24 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
           <t>Q</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <r>
+            <t>R30Q</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>47</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="57"/>
     <row r="58">
@@ -2986,6 +3027,11 @@
       <c r="P58" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q58" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3095,17 +3141,19 @@
           <t>G</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <r>
+            <t>S24G</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>60</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="61"/>
     <row r="62">
@@ -3165,6 +3213,11 @@
       <c r="P62" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q62" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3269,22 +3322,24 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <r>
+            <t>L30M</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>NA</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="65"/>
     <row r="66">
@@ -3344,6 +3399,11 @@
       <c r="P66" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q66" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3448,18 +3508,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
-      <c r="P68" t="inlineStr"/>
     </row>
     <row r="69"/>
     <row r="70">
@@ -3519,6 +3567,11 @@
       <c r="P70" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q70" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3628,17 +3681,19 @@
           <t>S</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr"/>
-      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <r>
+            <t>A24S</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>100</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="73"/>
     <row r="74">
@@ -3698,6 +3753,11 @@
       <c r="P74" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q74" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3802,18 +3862,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr"/>
-      <c r="P76" t="inlineStr"/>
     </row>
     <row r="77"/>
     <row r="78">
@@ -3873,6 +3921,11 @@
       <c r="P78" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q78" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3977,22 +4030,24 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
-      <c r="O80" t="inlineStr"/>
-      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <r>
+            <t>R29K</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>NA</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="81"/>
     <row r="82">
@@ -4052,6 +4107,11 @@
       <c r="P82" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q82" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4156,18 +4216,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
-      <c r="O84" t="inlineStr"/>
-      <c r="P84" t="inlineStr"/>
     </row>
     <row r="85"/>
     <row r="86">
@@ -4227,6 +4275,11 @@
       <c r="P86" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q86" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4331,18 +4384,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
-      <c r="O88" t="inlineStr"/>
-      <c r="P88" t="inlineStr"/>
     </row>
     <row r="89"/>
     <row r="90">
@@ -4402,6 +4443,11 @@
       <c r="P90" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q90" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4506,22 +4552,24 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="O92" t="inlineStr"/>
-      <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <r>
+            <t>V62I</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>NA</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="93"/>
     <row r="94">
@@ -4581,6 +4629,11 @@
       <c r="P94" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q94" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4685,18 +4738,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
-      <c r="O96" t="inlineStr"/>
-      <c r="P96" t="inlineStr"/>
     </row>
     <row r="97"/>
     <row r="98">
@@ -4756,6 +4797,11 @@
       <c r="P98" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q98" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4860,18 +4906,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
-      <c r="O100" t="inlineStr"/>
-      <c r="P100" t="inlineStr"/>
     </row>
     <row r="101"/>
     <row r="102">
@@ -4931,6 +4965,11 @@
       <c r="P102" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q102" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -5040,21 +5079,36 @@
           <t>S</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr"/>
       <c r="N104" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="O104" t="inlineStr"/>
-      <c r="P104" t="inlineStr"/>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <r>
+            <t>T24S</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>100</t>
+          </r>
+          <r>
+            <t xml:space="preserve">, </t>
+          </r>
+          <r>
+            <t>V62I</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>NA</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="105"/>
     <row r="106">
@@ -5114,6 +5168,11 @@
       <c r="P106" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q106" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -5218,18 +5277,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr"/>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr"/>
-      <c r="N108" t="inlineStr"/>
-      <c r="O108" t="inlineStr"/>
-      <c r="P108" t="inlineStr"/>
     </row>
     <row r="109"/>
     <row r="110">
@@ -5289,6 +5336,11 @@
       <c r="P110" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q110" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -5393,22 +5445,24 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr"/>
-      <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr"/>
-      <c r="N112" t="inlineStr"/>
-      <c r="O112" t="inlineStr"/>
-      <c r="P112" t="inlineStr"/>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <r>
+            <t>K29R</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>NA</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="113"/>
     <row r="114">
@@ -5468,6 +5522,11 @@
       <c r="P114" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q114" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -5572,22 +5631,24 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr"/>
-      <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr"/>
-      <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
-      <c r="O116" t="inlineStr"/>
-      <c r="P116" t="inlineStr"/>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <r>
+            <t>L30M</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>NA</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="117"/>
     <row r="118">
@@ -5647,6 +5708,11 @@
       <c r="P118" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q118" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -5751,18 +5817,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr"/>
-      <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr"/>
-      <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
-      <c r="O120" t="inlineStr"/>
-      <c r="P120" t="inlineStr"/>
     </row>
     <row r="121"/>
     <row r="122">
@@ -5822,6 +5876,11 @@
       <c r="P122" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q122" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -5926,18 +5985,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr"/>
-      <c r="F124" t="inlineStr"/>
-      <c r="G124" t="inlineStr"/>
-      <c r="H124" t="inlineStr"/>
-      <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
-      <c r="O124" t="inlineStr"/>
-      <c r="P124" t="inlineStr"/>
     </row>
     <row r="125"/>
     <row r="126">
@@ -5997,6 +6044,11 @@
       <c r="P126" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q126" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -6101,18 +6153,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr"/>
-      <c r="G128" t="inlineStr"/>
-      <c r="H128" t="inlineStr"/>
-      <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
-      <c r="O128" t="inlineStr"/>
-      <c r="P128" t="inlineStr"/>
     </row>
     <row r="129"/>
     <row r="130">
@@ -6172,6 +6212,11 @@
       <c r="P130" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q130" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -6276,26 +6321,41 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr"/>
-      <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
-      <c r="O132" t="inlineStr"/>
-      <c r="P132" t="inlineStr"/>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <r>
+            <t>V29M</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>NA</t>
+          </r>
+          <r>
+            <t xml:space="preserve">, </t>
+          </r>
+          <r>
+            <t>I32V</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>NA</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="133"/>
     <row r="134">
@@ -6355,6 +6415,11 @@
       <c r="P134" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q134" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -6464,17 +6529,19 @@
           <t>S</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr"/>
-      <c r="G136" t="inlineStr"/>
-      <c r="H136" t="inlineStr"/>
-      <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
-      <c r="K136" t="inlineStr"/>
-      <c r="L136" t="inlineStr"/>
-      <c r="M136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
-      <c r="O136" t="inlineStr"/>
-      <c r="P136" t="inlineStr"/>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <r>
+            <t>T24S</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>86</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="137"/>
     <row r="138">
@@ -6534,6 +6601,11 @@
       <c r="P138" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q138" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -6638,22 +6710,24 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr"/>
-      <c r="F140" t="inlineStr"/>
-      <c r="G140" t="inlineStr"/>
-      <c r="H140" t="inlineStr"/>
-      <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
-      <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
-      <c r="O140" t="inlineStr"/>
-      <c r="P140" t="inlineStr"/>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <r>
+            <t>V31M</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>57</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="141"/>
     <row r="142">
@@ -6713,6 +6787,11 @@
       <c r="P142" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q142" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -6817,18 +6896,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E144" t="inlineStr"/>
-      <c r="F144" t="inlineStr"/>
-      <c r="G144" t="inlineStr"/>
-      <c r="H144" t="inlineStr"/>
-      <c r="I144" t="inlineStr"/>
-      <c r="J144" t="inlineStr"/>
-      <c r="K144" t="inlineStr"/>
-      <c r="L144" t="inlineStr"/>
-      <c r="M144" t="inlineStr"/>
-      <c r="N144" t="inlineStr"/>
-      <c r="O144" t="inlineStr"/>
-      <c r="P144" t="inlineStr"/>
     </row>
     <row r="145"/>
     <row r="146">
@@ -6888,6 +6955,11 @@
       <c r="P146" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q146" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -6992,18 +7064,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr"/>
-      <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr"/>
-      <c r="H148" t="inlineStr"/>
-      <c r="I148" t="inlineStr"/>
-      <c r="J148" t="inlineStr"/>
-      <c r="K148" t="inlineStr"/>
-      <c r="L148" t="inlineStr"/>
-      <c r="M148" t="inlineStr"/>
-      <c r="N148" t="inlineStr"/>
-      <c r="O148" t="inlineStr"/>
-      <c r="P148" t="inlineStr"/>
     </row>
     <row r="149"/>
     <row r="150">
@@ -7063,6 +7123,11 @@
       <c r="P150" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q150" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -7167,22 +7232,24 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E152" t="inlineStr"/>
-      <c r="F152" t="inlineStr"/>
       <c r="G152" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr"/>
-      <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
-      <c r="K152" t="inlineStr"/>
-      <c r="L152" t="inlineStr"/>
-      <c r="M152" t="inlineStr"/>
-      <c r="N152" t="inlineStr"/>
-      <c r="O152" t="inlineStr"/>
-      <c r="P152" t="inlineStr"/>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <r>
+            <t>R28K</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>NA</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="153"/>
     <row r="154">
@@ -7242,6 +7309,11 @@
       <c r="P154" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q154" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -7346,18 +7418,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E156" t="inlineStr"/>
-      <c r="F156" t="inlineStr"/>
-      <c r="G156" t="inlineStr"/>
-      <c r="H156" t="inlineStr"/>
-      <c r="I156" t="inlineStr"/>
-      <c r="J156" t="inlineStr"/>
-      <c r="K156" t="inlineStr"/>
-      <c r="L156" t="inlineStr"/>
-      <c r="M156" t="inlineStr"/>
-      <c r="N156" t="inlineStr"/>
-      <c r="O156" t="inlineStr"/>
-      <c r="P156" t="inlineStr"/>
     </row>
     <row r="157"/>
     <row r="158">
@@ -7417,6 +7477,11 @@
       <c r="P158" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q158" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -7521,18 +7586,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr"/>
-      <c r="F160" t="inlineStr"/>
-      <c r="G160" t="inlineStr"/>
-      <c r="H160" t="inlineStr"/>
-      <c r="I160" t="inlineStr"/>
-      <c r="J160" t="inlineStr"/>
-      <c r="K160" t="inlineStr"/>
-      <c r="L160" t="inlineStr"/>
-      <c r="M160" t="inlineStr"/>
-      <c r="N160" t="inlineStr"/>
-      <c r="O160" t="inlineStr"/>
-      <c r="P160" t="inlineStr"/>
     </row>
     <row r="161"/>
     <row r="162">
@@ -7592,6 +7645,11 @@
       <c r="P162" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q162" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -7696,26 +7754,41 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E164" t="inlineStr"/>
-      <c r="F164" t="inlineStr"/>
       <c r="G164" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr"/>
-      <c r="I164" t="inlineStr"/>
-      <c r="J164" t="inlineStr"/>
-      <c r="K164" t="inlineStr"/>
-      <c r="L164" t="inlineStr"/>
-      <c r="M164" t="inlineStr"/>
       <c r="N164" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="O164" t="inlineStr"/>
-      <c r="P164" t="inlineStr"/>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <r>
+            <t>V28L</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>93</t>
+          </r>
+          <r>
+            <t xml:space="preserve">, </t>
+          </r>
+          <r>
+            <t>D62E</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>84</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="165"/>
     <row r="166">
@@ -7775,6 +7848,11 @@
       <c r="P166" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q166" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -7879,18 +7957,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E168" t="inlineStr"/>
-      <c r="F168" t="inlineStr"/>
-      <c r="G168" t="inlineStr"/>
-      <c r="H168" t="inlineStr"/>
-      <c r="I168" t="inlineStr"/>
-      <c r="J168" t="inlineStr"/>
-      <c r="K168" t="inlineStr"/>
-      <c r="L168" t="inlineStr"/>
-      <c r="M168" t="inlineStr"/>
-      <c r="N168" t="inlineStr"/>
-      <c r="O168" t="inlineStr"/>
-      <c r="P168" t="inlineStr"/>
     </row>
     <row r="169"/>
     <row r="170">
@@ -7950,6 +8016,11 @@
       <c r="P170" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q170" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -8054,18 +8125,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E172" t="inlineStr"/>
-      <c r="F172" t="inlineStr"/>
-      <c r="G172" t="inlineStr"/>
-      <c r="H172" t="inlineStr"/>
-      <c r="I172" t="inlineStr"/>
-      <c r="J172" t="inlineStr"/>
-      <c r="K172" t="inlineStr"/>
-      <c r="L172" t="inlineStr"/>
-      <c r="M172" t="inlineStr"/>
-      <c r="N172" t="inlineStr"/>
-      <c r="O172" t="inlineStr"/>
-      <c r="P172" t="inlineStr"/>
     </row>
     <row r="173"/>
     <row r="174">
@@ -8125,6 +8184,11 @@
       <c r="P174" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q174" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -8229,22 +8293,24 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E176" t="inlineStr"/>
-      <c r="F176" t="inlineStr"/>
-      <c r="G176" t="inlineStr"/>
-      <c r="H176" t="inlineStr"/>
-      <c r="I176" t="inlineStr"/>
-      <c r="J176" t="inlineStr"/>
       <c r="K176" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="L176" t="inlineStr"/>
-      <c r="M176" t="inlineStr"/>
-      <c r="N176" t="inlineStr"/>
-      <c r="O176" t="inlineStr"/>
-      <c r="P176" t="inlineStr"/>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <r>
+            <t>V32I</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>NA</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="177"/>
     <row r="178">
@@ -8304,6 +8370,11 @@
       <c r="P178" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q178" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -8408,18 +8479,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E180" t="inlineStr"/>
-      <c r="F180" t="inlineStr"/>
-      <c r="G180" t="inlineStr"/>
-      <c r="H180" t="inlineStr"/>
-      <c r="I180" t="inlineStr"/>
-      <c r="J180" t="inlineStr"/>
-      <c r="K180" t="inlineStr"/>
-      <c r="L180" t="inlineStr"/>
-      <c r="M180" t="inlineStr"/>
-      <c r="N180" t="inlineStr"/>
-      <c r="O180" t="inlineStr"/>
-      <c r="P180" t="inlineStr"/>
     </row>
     <row r="181"/>
     <row r="182">
@@ -8479,6 +8538,11 @@
       <c r="P182" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q182" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -8583,26 +8647,41 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E184" t="inlineStr"/>
-      <c r="F184" t="inlineStr"/>
       <c r="G184" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr"/>
-      <c r="I184" t="inlineStr"/>
-      <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="L184" t="inlineStr"/>
-      <c r="M184" t="inlineStr"/>
-      <c r="N184" t="inlineStr"/>
-      <c r="O184" t="inlineStr"/>
-      <c r="P184" t="inlineStr"/>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <r>
+            <t>Q28R</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>NA</t>
+          </r>
+          <r>
+            <t xml:space="preserve">, </t>
+          </r>
+          <r>
+            <t>V32I</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>NA</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="185"/>
     <row r="186">
@@ -8662,6 +8741,11 @@
       <c r="P186" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q186" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -8766,22 +8850,24 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E188" t="inlineStr"/>
-      <c r="F188" t="inlineStr"/>
       <c r="G188" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="H188" t="inlineStr"/>
-      <c r="I188" t="inlineStr"/>
-      <c r="J188" t="inlineStr"/>
-      <c r="K188" t="inlineStr"/>
-      <c r="L188" t="inlineStr"/>
-      <c r="M188" t="inlineStr"/>
-      <c r="N188" t="inlineStr"/>
-      <c r="O188" t="inlineStr"/>
-      <c r="P188" t="inlineStr"/>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <r>
+            <t>Q28R</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>NA</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="189"/>
     <row r="190">
@@ -8841,6 +8927,11 @@
       <c r="P190" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q190" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -8945,18 +9036,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E192" t="inlineStr"/>
-      <c r="F192" t="inlineStr"/>
-      <c r="G192" t="inlineStr"/>
-      <c r="H192" t="inlineStr"/>
-      <c r="I192" t="inlineStr"/>
-      <c r="J192" t="inlineStr"/>
-      <c r="K192" t="inlineStr"/>
-      <c r="L192" t="inlineStr"/>
-      <c r="M192" t="inlineStr"/>
-      <c r="N192" t="inlineStr"/>
-      <c r="O192" t="inlineStr"/>
-      <c r="P192" t="inlineStr"/>
     </row>
     <row r="193"/>
     <row r="194">
@@ -9016,6 +9095,11 @@
       <c r="P194" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q194" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -9120,18 +9204,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E196" t="inlineStr"/>
-      <c r="F196" t="inlineStr"/>
-      <c r="G196" t="inlineStr"/>
-      <c r="H196" t="inlineStr"/>
-      <c r="I196" t="inlineStr"/>
-      <c r="J196" t="inlineStr"/>
-      <c r="K196" t="inlineStr"/>
-      <c r="L196" t="inlineStr"/>
-      <c r="M196" t="inlineStr"/>
-      <c r="N196" t="inlineStr"/>
-      <c r="O196" t="inlineStr"/>
-      <c r="P196" t="inlineStr"/>
     </row>
     <row r="197"/>
     <row r="198">
@@ -9191,6 +9263,11 @@
       <c r="P198" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q198" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -9295,22 +9372,24 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E200" t="inlineStr"/>
-      <c r="F200" t="inlineStr"/>
-      <c r="G200" t="inlineStr"/>
       <c r="H200" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I200" t="inlineStr"/>
-      <c r="J200" t="inlineStr"/>
-      <c r="K200" t="inlineStr"/>
-      <c r="L200" t="inlineStr"/>
-      <c r="M200" t="inlineStr"/>
-      <c r="N200" t="inlineStr"/>
-      <c r="O200" t="inlineStr"/>
-      <c r="P200" t="inlineStr"/>
+      <c r="Q200" t="inlineStr">
+        <is>
+          <r>
+            <t>M29L</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>NA</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="201"/>
     <row r="202">
@@ -9370,6 +9449,11 @@
       <c r="P202" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q202" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -9474,18 +9558,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E204" t="inlineStr"/>
-      <c r="F204" t="inlineStr"/>
-      <c r="G204" t="inlineStr"/>
-      <c r="H204" t="inlineStr"/>
-      <c r="I204" t="inlineStr"/>
-      <c r="J204" t="inlineStr"/>
-      <c r="K204" t="inlineStr"/>
-      <c r="L204" t="inlineStr"/>
-      <c r="M204" t="inlineStr"/>
-      <c r="N204" t="inlineStr"/>
-      <c r="O204" t="inlineStr"/>
-      <c r="P204" t="inlineStr"/>
     </row>
     <row r="205"/>
     <row r="206">
@@ -9545,6 +9617,11 @@
       <c r="P206" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q206" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -9649,18 +9726,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E208" t="inlineStr"/>
-      <c r="F208" t="inlineStr"/>
-      <c r="G208" t="inlineStr"/>
-      <c r="H208" t="inlineStr"/>
-      <c r="I208" t="inlineStr"/>
-      <c r="J208" t="inlineStr"/>
-      <c r="K208" t="inlineStr"/>
-      <c r="L208" t="inlineStr"/>
-      <c r="M208" t="inlineStr"/>
-      <c r="N208" t="inlineStr"/>
-      <c r="O208" t="inlineStr"/>
-      <c r="P208" t="inlineStr"/>
     </row>
     <row r="209"/>
     <row r="210">
@@ -9720,6 +9785,11 @@
       <c r="P210" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q210" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -9824,18 +9894,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E212" t="inlineStr"/>
-      <c r="F212" t="inlineStr"/>
-      <c r="G212" t="inlineStr"/>
-      <c r="H212" t="inlineStr"/>
-      <c r="I212" t="inlineStr"/>
-      <c r="J212" t="inlineStr"/>
-      <c r="K212" t="inlineStr"/>
-      <c r="L212" t="inlineStr"/>
-      <c r="M212" t="inlineStr"/>
-      <c r="N212" t="inlineStr"/>
-      <c r="O212" t="inlineStr"/>
-      <c r="P212" t="inlineStr"/>
     </row>
     <row r="213"/>
     <row r="214">
@@ -9895,6 +9953,11 @@
       <c r="P214" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q214" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -9999,18 +10062,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E216" t="inlineStr"/>
-      <c r="F216" t="inlineStr"/>
-      <c r="G216" t="inlineStr"/>
-      <c r="H216" t="inlineStr"/>
-      <c r="I216" t="inlineStr"/>
-      <c r="J216" t="inlineStr"/>
-      <c r="K216" t="inlineStr"/>
-      <c r="L216" t="inlineStr"/>
-      <c r="M216" t="inlineStr"/>
-      <c r="N216" t="inlineStr"/>
-      <c r="O216" t="inlineStr"/>
-      <c r="P216" t="inlineStr"/>
     </row>
     <row r="217"/>
     <row r="218">
@@ -10070,6 +10121,11 @@
       <c r="P218" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q218" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -10174,18 +10230,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E220" t="inlineStr"/>
-      <c r="F220" t="inlineStr"/>
-      <c r="G220" t="inlineStr"/>
-      <c r="H220" t="inlineStr"/>
-      <c r="I220" t="inlineStr"/>
-      <c r="J220" t="inlineStr"/>
-      <c r="K220" t="inlineStr"/>
-      <c r="L220" t="inlineStr"/>
-      <c r="M220" t="inlineStr"/>
-      <c r="N220" t="inlineStr"/>
-      <c r="O220" t="inlineStr"/>
-      <c r="P220" t="inlineStr"/>
     </row>
     <row r="221"/>
     <row r="222">
@@ -10245,6 +10289,11 @@
       <c r="P222" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q222" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -10349,22 +10398,24 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E224" t="inlineStr"/>
-      <c r="F224" t="inlineStr"/>
-      <c r="G224" t="inlineStr"/>
-      <c r="H224" t="inlineStr"/>
-      <c r="I224" t="inlineStr"/>
-      <c r="J224" t="inlineStr"/>
       <c r="K224" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="L224" t="inlineStr"/>
-      <c r="M224" t="inlineStr"/>
-      <c r="N224" t="inlineStr"/>
-      <c r="O224" t="inlineStr"/>
-      <c r="P224" t="inlineStr"/>
+      <c r="Q224" t="inlineStr">
+        <is>
+          <r>
+            <t>I32V</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>NA</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="225"/>
     <row r="226">
@@ -10424,6 +10475,11 @@
       <c r="P226" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q226" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -10528,22 +10584,24 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E228" t="inlineStr"/>
       <c r="F228" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="G228" t="inlineStr"/>
-      <c r="H228" t="inlineStr"/>
-      <c r="I228" t="inlineStr"/>
-      <c r="J228" t="inlineStr"/>
-      <c r="K228" t="inlineStr"/>
-      <c r="L228" t="inlineStr"/>
-      <c r="M228" t="inlineStr"/>
-      <c r="N228" t="inlineStr"/>
-      <c r="O228" t="inlineStr"/>
-      <c r="P228" t="inlineStr"/>
+      <c r="Q228" t="inlineStr">
+        <is>
+          <r>
+            <t>I26M</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>NA</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="229"/>
     <row r="230">
@@ -10603,6 +10661,11 @@
       <c r="P230" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q230" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -10707,22 +10770,24 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E232" t="inlineStr"/>
-      <c r="F232" t="inlineStr"/>
-      <c r="G232" t="inlineStr"/>
-      <c r="H232" t="inlineStr"/>
-      <c r="I232" t="inlineStr"/>
-      <c r="J232" t="inlineStr"/>
       <c r="K232" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="L232" t="inlineStr"/>
-      <c r="M232" t="inlineStr"/>
-      <c r="N232" t="inlineStr"/>
-      <c r="O232" t="inlineStr"/>
-      <c r="P232" t="inlineStr"/>
+      <c r="Q232" t="inlineStr">
+        <is>
+          <r>
+            <t>L32I</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>NA</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="233"/>
     <row r="234">
@@ -10782,6 +10847,11 @@
       <c r="P234" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q234" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -10886,22 +10956,24 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E236" t="inlineStr"/>
-      <c r="F236" t="inlineStr"/>
-      <c r="G236" t="inlineStr"/>
-      <c r="H236" t="inlineStr"/>
-      <c r="I236" t="inlineStr"/>
-      <c r="J236" t="inlineStr"/>
-      <c r="K236" t="inlineStr"/>
-      <c r="L236" t="inlineStr"/>
-      <c r="M236" t="inlineStr"/>
       <c r="N236" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="O236" t="inlineStr"/>
-      <c r="P236" t="inlineStr"/>
+      <c r="Q236" t="inlineStr">
+        <is>
+          <r>
+            <t>Q62E</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>88</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="237"/>
     <row r="238">
@@ -10961,6 +11033,11 @@
       <c r="P238" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q238" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -11065,18 +11142,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E240" t="inlineStr"/>
-      <c r="F240" t="inlineStr"/>
-      <c r="G240" t="inlineStr"/>
-      <c r="H240" t="inlineStr"/>
-      <c r="I240" t="inlineStr"/>
-      <c r="J240" t="inlineStr"/>
-      <c r="K240" t="inlineStr"/>
-      <c r="L240" t="inlineStr"/>
-      <c r="M240" t="inlineStr"/>
-      <c r="N240" t="inlineStr"/>
-      <c r="O240" t="inlineStr"/>
-      <c r="P240" t="inlineStr"/>
     </row>
     <row r="241"/>
     <row r="242">
@@ -11136,6 +11201,11 @@
       <c r="P242" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q242" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -11240,18 +11310,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E244" t="inlineStr"/>
-      <c r="F244" t="inlineStr"/>
-      <c r="G244" t="inlineStr"/>
-      <c r="H244" t="inlineStr"/>
-      <c r="I244" t="inlineStr"/>
-      <c r="J244" t="inlineStr"/>
-      <c r="K244" t="inlineStr"/>
-      <c r="L244" t="inlineStr"/>
-      <c r="M244" t="inlineStr"/>
-      <c r="N244" t="inlineStr"/>
-      <c r="O244" t="inlineStr"/>
-      <c r="P244" t="inlineStr"/>
     </row>
     <row r="245"/>
     <row r="246">
@@ -11311,6 +11369,11 @@
       <c r="P246" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q246" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -11415,18 +11478,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E248" t="inlineStr"/>
-      <c r="F248" t="inlineStr"/>
-      <c r="G248" t="inlineStr"/>
-      <c r="H248" t="inlineStr"/>
-      <c r="I248" t="inlineStr"/>
-      <c r="J248" t="inlineStr"/>
-      <c r="K248" t="inlineStr"/>
-      <c r="L248" t="inlineStr"/>
-      <c r="M248" t="inlineStr"/>
-      <c r="N248" t="inlineStr"/>
-      <c r="O248" t="inlineStr"/>
-      <c r="P248" t="inlineStr"/>
     </row>
     <row r="249"/>
     <row r="250">
@@ -11486,6 +11537,11 @@
       <c r="P250" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q250" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -11590,18 +11646,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E252" t="inlineStr"/>
-      <c r="F252" t="inlineStr"/>
-      <c r="G252" t="inlineStr"/>
-      <c r="H252" t="inlineStr"/>
-      <c r="I252" t="inlineStr"/>
-      <c r="J252" t="inlineStr"/>
-      <c r="K252" t="inlineStr"/>
-      <c r="L252" t="inlineStr"/>
-      <c r="M252" t="inlineStr"/>
-      <c r="N252" t="inlineStr"/>
-      <c r="O252" t="inlineStr"/>
-      <c r="P252" t="inlineStr"/>
     </row>
     <row r="253"/>
     <row r="254">
@@ -11661,6 +11705,11 @@
       <c r="P254" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q254" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -11765,22 +11814,24 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E256" t="inlineStr"/>
-      <c r="F256" t="inlineStr"/>
       <c r="G256" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="H256" t="inlineStr"/>
-      <c r="I256" t="inlineStr"/>
-      <c r="J256" t="inlineStr"/>
-      <c r="K256" t="inlineStr"/>
-      <c r="L256" t="inlineStr"/>
-      <c r="M256" t="inlineStr"/>
-      <c r="N256" t="inlineStr"/>
-      <c r="O256" t="inlineStr"/>
-      <c r="P256" t="inlineStr"/>
+      <c r="Q256" t="inlineStr">
+        <is>
+          <r>
+            <t>F28L</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>71</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="257"/>
     <row r="258">
@@ -11840,6 +11891,11 @@
       <c r="P258" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q258" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -11944,22 +12000,24 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E260" t="inlineStr"/>
-      <c r="F260" t="inlineStr"/>
       <c r="G260" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="H260" t="inlineStr"/>
-      <c r="I260" t="inlineStr"/>
-      <c r="J260" t="inlineStr"/>
-      <c r="K260" t="inlineStr"/>
-      <c r="L260" t="inlineStr"/>
-      <c r="M260" t="inlineStr"/>
-      <c r="N260" t="inlineStr"/>
-      <c r="O260" t="inlineStr"/>
-      <c r="P260" t="inlineStr"/>
+      <c r="Q260" t="inlineStr">
+        <is>
+          <r>
+            <t>F28L</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>71</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="261"/>
     <row r="262">
@@ -12019,6 +12077,11 @@
       <c r="P262" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q262" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -12123,18 +12186,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E264" t="inlineStr"/>
-      <c r="F264" t="inlineStr"/>
-      <c r="G264" t="inlineStr"/>
-      <c r="H264" t="inlineStr"/>
-      <c r="I264" t="inlineStr"/>
-      <c r="J264" t="inlineStr"/>
-      <c r="K264" t="inlineStr"/>
-      <c r="L264" t="inlineStr"/>
-      <c r="M264" t="inlineStr"/>
-      <c r="N264" t="inlineStr"/>
-      <c r="O264" t="inlineStr"/>
-      <c r="P264" t="inlineStr"/>
     </row>
     <row r="265"/>
     <row r="266">
@@ -12194,6 +12245,11 @@
       <c r="P266" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q266" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -12298,18 +12354,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E268" t="inlineStr"/>
-      <c r="F268" t="inlineStr"/>
-      <c r="G268" t="inlineStr"/>
-      <c r="H268" t="inlineStr"/>
-      <c r="I268" t="inlineStr"/>
-      <c r="J268" t="inlineStr"/>
-      <c r="K268" t="inlineStr"/>
-      <c r="L268" t="inlineStr"/>
-      <c r="M268" t="inlineStr"/>
-      <c r="N268" t="inlineStr"/>
-      <c r="O268" t="inlineStr"/>
-      <c r="P268" t="inlineStr"/>
     </row>
     <row r="269"/>
     <row r="270">
@@ -12369,6 +12413,11 @@
       <c r="P270" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q270" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -12473,22 +12522,24 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E272" t="inlineStr"/>
-      <c r="F272" t="inlineStr"/>
       <c r="G272" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H272" t="inlineStr"/>
-      <c r="I272" t="inlineStr"/>
-      <c r="J272" t="inlineStr"/>
-      <c r="K272" t="inlineStr"/>
-      <c r="L272" t="inlineStr"/>
-      <c r="M272" t="inlineStr"/>
-      <c r="N272" t="inlineStr"/>
-      <c r="O272" t="inlineStr"/>
-      <c r="P272" t="inlineStr"/>
+      <c r="Q272" t="inlineStr">
+        <is>
+          <r>
+            <t>T28A</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>NA</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="273"/>
     <row r="274">
@@ -12548,6 +12599,11 @@
       <c r="P274" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q274" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -12652,22 +12708,24 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E276" t="inlineStr"/>
-      <c r="F276" t="inlineStr"/>
-      <c r="G276" t="inlineStr"/>
-      <c r="H276" t="inlineStr"/>
-      <c r="I276" t="inlineStr"/>
-      <c r="J276" t="inlineStr"/>
-      <c r="K276" t="inlineStr"/>
-      <c r="L276" t="inlineStr"/>
-      <c r="M276" t="inlineStr"/>
       <c r="N276" t="inlineStr">
         <is>
           <t>Q</t>
         </is>
       </c>
-      <c r="O276" t="inlineStr"/>
-      <c r="P276" t="inlineStr"/>
+      <c r="Q276" t="inlineStr">
+        <is>
+          <r>
+            <t>A62Q</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>35</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="277"/>
     <row r="278">
@@ -12727,6 +12785,11 @@
       <c r="P278" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q278" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -12831,18 +12894,11 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E280" t="inlineStr"/>
-      <c r="F280" t="inlineStr"/>
       <c r="G280" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="H280" t="inlineStr"/>
-      <c r="I280" t="inlineStr"/>
-      <c r="J280" t="inlineStr"/>
-      <c r="K280" t="inlineStr"/>
-      <c r="L280" t="inlineStr"/>
       <c r="M280" t="inlineStr">
         <is>
           <t>P</t>
@@ -12853,8 +12909,43 @@
           <t>T</t>
         </is>
       </c>
-      <c r="O280" t="inlineStr"/>
-      <c r="P280" t="inlineStr"/>
+      <c r="Q280" t="inlineStr">
+        <is>
+          <r>
+            <t>A28T</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>65</t>
+          </r>
+          <r>
+            <t xml:space="preserve">, </t>
+          </r>
+          <r>
+            <t>S58P</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>79</t>
+          </r>
+          <r>
+            <t xml:space="preserve">, </t>
+          </r>
+          <r>
+            <t>A62T</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>45</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="281"/>
     <row r="282">
@@ -12914,6 +13005,11 @@
       <c r="P282" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q282" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -13023,17 +13119,19 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F284" t="inlineStr"/>
-      <c r="G284" t="inlineStr"/>
-      <c r="H284" t="inlineStr"/>
-      <c r="I284" t="inlineStr"/>
-      <c r="J284" t="inlineStr"/>
-      <c r="K284" t="inlineStr"/>
-      <c r="L284" t="inlineStr"/>
-      <c r="M284" t="inlineStr"/>
-      <c r="N284" t="inlineStr"/>
-      <c r="O284" t="inlineStr"/>
-      <c r="P284" t="inlineStr"/>
+      <c r="Q284" t="inlineStr">
+        <is>
+          <r>
+            <t>S24A</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>NA</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="285"/>
     <row r="286">
@@ -13093,6 +13191,11 @@
       <c r="P286" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q286" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -13197,18 +13300,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E288" t="inlineStr"/>
-      <c r="F288" t="inlineStr"/>
-      <c r="G288" t="inlineStr"/>
-      <c r="H288" t="inlineStr"/>
-      <c r="I288" t="inlineStr"/>
-      <c r="J288" t="inlineStr"/>
-      <c r="K288" t="inlineStr"/>
-      <c r="L288" t="inlineStr"/>
-      <c r="M288" t="inlineStr"/>
-      <c r="N288" t="inlineStr"/>
-      <c r="O288" t="inlineStr"/>
-      <c r="P288" t="inlineStr"/>
     </row>
     <row r="289"/>
     <row r="290">
@@ -13268,6 +13359,11 @@
       <c r="P290" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q290" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -13295,7 +13391,6 @@
           <t>R</t>
         </is>
       </c>
-      <c r="F291" t="inlineStr"/>
       <c r="G291" t="inlineStr">
         <is>
           <t>A</t>
@@ -13373,17 +13468,19 @@
           <t>K</t>
         </is>
       </c>
-      <c r="F292" t="inlineStr"/>
-      <c r="G292" t="inlineStr"/>
-      <c r="H292" t="inlineStr"/>
-      <c r="I292" t="inlineStr"/>
-      <c r="J292" t="inlineStr"/>
-      <c r="K292" t="inlineStr"/>
-      <c r="L292" t="inlineStr"/>
-      <c r="M292" t="inlineStr"/>
-      <c r="N292" t="inlineStr"/>
-      <c r="O292" t="inlineStr"/>
-      <c r="P292" t="inlineStr"/>
+      <c r="Q292" t="inlineStr">
+        <is>
+          <r>
+            <t>R24K</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>100</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="293"/>
     <row r="294">
@@ -13443,6 +13540,11 @@
       <c r="P294" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q294" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -13547,18 +13649,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E296" t="inlineStr"/>
-      <c r="F296" t="inlineStr"/>
-      <c r="G296" t="inlineStr"/>
-      <c r="H296" t="inlineStr"/>
-      <c r="I296" t="inlineStr"/>
-      <c r="J296" t="inlineStr"/>
-      <c r="K296" t="inlineStr"/>
-      <c r="L296" t="inlineStr"/>
-      <c r="M296" t="inlineStr"/>
-      <c r="N296" t="inlineStr"/>
-      <c r="O296" t="inlineStr"/>
-      <c r="P296" t="inlineStr"/>
     </row>
     <row r="297"/>
     <row r="298">
@@ -13618,6 +13708,11 @@
       <c r="P298" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q298" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -13722,18 +13817,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E300" t="inlineStr"/>
-      <c r="F300" t="inlineStr"/>
-      <c r="G300" t="inlineStr"/>
-      <c r="H300" t="inlineStr"/>
-      <c r="I300" t="inlineStr"/>
-      <c r="J300" t="inlineStr"/>
-      <c r="K300" t="inlineStr"/>
-      <c r="L300" t="inlineStr"/>
-      <c r="M300" t="inlineStr"/>
-      <c r="N300" t="inlineStr"/>
-      <c r="O300" t="inlineStr"/>
-      <c r="P300" t="inlineStr"/>
     </row>
     <row r="301"/>
     <row r="302">
@@ -13793,6 +13876,11 @@
       <c r="P302" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q302" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -13897,18 +13985,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E304" t="inlineStr"/>
-      <c r="F304" t="inlineStr"/>
-      <c r="G304" t="inlineStr"/>
-      <c r="H304" t="inlineStr"/>
-      <c r="I304" t="inlineStr"/>
-      <c r="J304" t="inlineStr"/>
-      <c r="K304" t="inlineStr"/>
-      <c r="L304" t="inlineStr"/>
-      <c r="M304" t="inlineStr"/>
-      <c r="N304" t="inlineStr"/>
-      <c r="O304" t="inlineStr"/>
-      <c r="P304" t="inlineStr"/>
     </row>
     <row r="305"/>
     <row r="306">
@@ -13968,6 +14044,11 @@
       <c r="P306" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q306" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -14072,18 +14153,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E308" t="inlineStr"/>
-      <c r="F308" t="inlineStr"/>
-      <c r="G308" t="inlineStr"/>
-      <c r="H308" t="inlineStr"/>
-      <c r="I308" t="inlineStr"/>
-      <c r="J308" t="inlineStr"/>
-      <c r="K308" t="inlineStr"/>
-      <c r="L308" t="inlineStr"/>
-      <c r="M308" t="inlineStr"/>
-      <c r="N308" t="inlineStr"/>
-      <c r="O308" t="inlineStr"/>
-      <c r="P308" t="inlineStr"/>
     </row>
     <row r="309"/>
     <row r="310">
@@ -14143,6 +14212,11 @@
       <c r="P310" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q310" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -14247,18 +14321,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E312" t="inlineStr"/>
-      <c r="F312" t="inlineStr"/>
-      <c r="G312" t="inlineStr"/>
-      <c r="H312" t="inlineStr"/>
-      <c r="I312" t="inlineStr"/>
-      <c r="J312" t="inlineStr"/>
-      <c r="K312" t="inlineStr"/>
-      <c r="L312" t="inlineStr"/>
-      <c r="M312" t="inlineStr"/>
-      <c r="N312" t="inlineStr"/>
-      <c r="O312" t="inlineStr"/>
-      <c r="P312" t="inlineStr"/>
     </row>
     <row r="313"/>
     <row r="314">
@@ -14318,6 +14380,11 @@
       <c r="P314" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q314" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -14422,18 +14489,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E316" t="inlineStr"/>
-      <c r="F316" t="inlineStr"/>
-      <c r="G316" t="inlineStr"/>
-      <c r="H316" t="inlineStr"/>
-      <c r="I316" t="inlineStr"/>
-      <c r="J316" t="inlineStr"/>
-      <c r="K316" t="inlineStr"/>
-      <c r="L316" t="inlineStr"/>
-      <c r="M316" t="inlineStr"/>
-      <c r="N316" t="inlineStr"/>
-      <c r="O316" t="inlineStr"/>
-      <c r="P316" t="inlineStr"/>
     </row>
     <row r="317"/>
     <row r="318">
@@ -14493,6 +14548,11 @@
       <c r="P318" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q318" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -14597,18 +14657,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E320" t="inlineStr"/>
-      <c r="F320" t="inlineStr"/>
-      <c r="G320" t="inlineStr"/>
-      <c r="H320" t="inlineStr"/>
-      <c r="I320" t="inlineStr"/>
-      <c r="J320" t="inlineStr"/>
-      <c r="K320" t="inlineStr"/>
-      <c r="L320" t="inlineStr"/>
-      <c r="M320" t="inlineStr"/>
-      <c r="N320" t="inlineStr"/>
-      <c r="O320" t="inlineStr"/>
-      <c r="P320" t="inlineStr"/>
     </row>
     <row r="321"/>
     <row r="322">
@@ -14668,6 +14716,11 @@
       <c r="P322" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q322" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -14772,18 +14825,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E324" t="inlineStr"/>
-      <c r="F324" t="inlineStr"/>
-      <c r="G324" t="inlineStr"/>
-      <c r="H324" t="inlineStr"/>
-      <c r="I324" t="inlineStr"/>
-      <c r="J324" t="inlineStr"/>
-      <c r="K324" t="inlineStr"/>
-      <c r="L324" t="inlineStr"/>
-      <c r="M324" t="inlineStr"/>
-      <c r="N324" t="inlineStr"/>
-      <c r="O324" t="inlineStr"/>
-      <c r="P324" t="inlineStr"/>
     </row>
     <row r="325"/>
     <row r="326">
@@ -14843,6 +14884,11 @@
       <c r="P326" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q326" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -14947,18 +14993,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E328" t="inlineStr"/>
-      <c r="F328" t="inlineStr"/>
-      <c r="G328" t="inlineStr"/>
-      <c r="H328" t="inlineStr"/>
-      <c r="I328" t="inlineStr"/>
-      <c r="J328" t="inlineStr"/>
-      <c r="K328" t="inlineStr"/>
-      <c r="L328" t="inlineStr"/>
-      <c r="M328" t="inlineStr"/>
-      <c r="N328" t="inlineStr"/>
-      <c r="O328" t="inlineStr"/>
-      <c r="P328" t="inlineStr"/>
     </row>
     <row r="329"/>
     <row r="330">
@@ -15018,6 +15052,11 @@
       <c r="P330" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q330" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -15122,22 +15161,24 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E332" t="inlineStr"/>
-      <c r="F332" t="inlineStr"/>
       <c r="G332" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="H332" t="inlineStr"/>
-      <c r="I332" t="inlineStr"/>
-      <c r="J332" t="inlineStr"/>
-      <c r="K332" t="inlineStr"/>
-      <c r="L332" t="inlineStr"/>
-      <c r="M332" t="inlineStr"/>
-      <c r="N332" t="inlineStr"/>
-      <c r="O332" t="inlineStr"/>
-      <c r="P332" t="inlineStr"/>
+      <c r="Q332" t="inlineStr">
+        <is>
+          <r>
+            <t>G28T</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>67</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="333"/>
     <row r="334">
@@ -15197,6 +15238,11 @@
       <c r="P334" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q334" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -15306,17 +15352,19 @@
           <t>K</t>
         </is>
       </c>
-      <c r="F336" t="inlineStr"/>
-      <c r="G336" t="inlineStr"/>
-      <c r="H336" t="inlineStr"/>
-      <c r="I336" t="inlineStr"/>
-      <c r="J336" t="inlineStr"/>
-      <c r="K336" t="inlineStr"/>
-      <c r="L336" t="inlineStr"/>
-      <c r="M336" t="inlineStr"/>
-      <c r="N336" t="inlineStr"/>
-      <c r="O336" t="inlineStr"/>
-      <c r="P336" t="inlineStr"/>
+      <c r="Q336" t="inlineStr">
+        <is>
+          <r>
+            <t>R24K</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>67</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="337"/>
     <row r="338">
@@ -15376,6 +15424,11 @@
       <c r="P338" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q338" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -15480,18 +15533,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E340" t="inlineStr"/>
-      <c r="F340" t="inlineStr"/>
-      <c r="G340" t="inlineStr"/>
-      <c r="H340" t="inlineStr"/>
-      <c r="I340" t="inlineStr"/>
-      <c r="J340" t="inlineStr"/>
-      <c r="K340" t="inlineStr"/>
-      <c r="L340" t="inlineStr"/>
-      <c r="M340" t="inlineStr"/>
-      <c r="N340" t="inlineStr"/>
-      <c r="O340" t="inlineStr"/>
-      <c r="P340" t="inlineStr"/>
     </row>
     <row r="341"/>
     <row r="342">
@@ -15551,6 +15592,11 @@
       <c r="P342" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q342" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -15655,18 +15701,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E344" t="inlineStr"/>
-      <c r="F344" t="inlineStr"/>
-      <c r="G344" t="inlineStr"/>
-      <c r="H344" t="inlineStr"/>
-      <c r="I344" t="inlineStr"/>
-      <c r="J344" t="inlineStr"/>
-      <c r="K344" t="inlineStr"/>
-      <c r="L344" t="inlineStr"/>
-      <c r="M344" t="inlineStr"/>
-      <c r="N344" t="inlineStr"/>
-      <c r="O344" t="inlineStr"/>
-      <c r="P344" t="inlineStr"/>
     </row>
     <row r="345"/>
     <row r="346">
@@ -15726,6 +15760,11 @@
       <c r="P346" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q346" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -15830,18 +15869,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E348" t="inlineStr"/>
-      <c r="F348" t="inlineStr"/>
-      <c r="G348" t="inlineStr"/>
-      <c r="H348" t="inlineStr"/>
-      <c r="I348" t="inlineStr"/>
-      <c r="J348" t="inlineStr"/>
-      <c r="K348" t="inlineStr"/>
-      <c r="L348" t="inlineStr"/>
-      <c r="M348" t="inlineStr"/>
-      <c r="N348" t="inlineStr"/>
-      <c r="O348" t="inlineStr"/>
-      <c r="P348" t="inlineStr"/>
     </row>
     <row r="349"/>
     <row r="350">
@@ -15901,6 +15928,11 @@
       <c r="P350" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q350" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -16005,22 +16037,24 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E352" t="inlineStr"/>
-      <c r="F352" t="inlineStr"/>
-      <c r="G352" t="inlineStr"/>
-      <c r="H352" t="inlineStr"/>
-      <c r="I352" t="inlineStr"/>
-      <c r="J352" t="inlineStr"/>
       <c r="K352" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="L352" t="inlineStr"/>
-      <c r="M352" t="inlineStr"/>
-      <c r="N352" t="inlineStr"/>
-      <c r="O352" t="inlineStr"/>
-      <c r="P352" t="inlineStr"/>
+      <c r="Q352" t="inlineStr">
+        <is>
+          <r>
+            <t>V32I</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>NA</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="353"/>
     <row r="354">
@@ -16080,6 +16114,11 @@
       <c r="P354" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q354" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -16184,26 +16223,41 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E356" t="inlineStr"/>
       <c r="F356" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="G356" t="inlineStr"/>
-      <c r="H356" t="inlineStr"/>
-      <c r="I356" t="inlineStr"/>
-      <c r="J356" t="inlineStr"/>
-      <c r="K356" t="inlineStr"/>
-      <c r="L356" t="inlineStr"/>
-      <c r="M356" t="inlineStr"/>
       <c r="N356" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="O356" t="inlineStr"/>
-      <c r="P356" t="inlineStr"/>
+      <c r="Q356" t="inlineStr">
+        <is>
+          <r>
+            <t>F26V</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>NA</t>
+          </r>
+          <r>
+            <t xml:space="preserve">, </t>
+          </r>
+          <r>
+            <t>A62T</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>24</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="357"/>
     <row r="358">
@@ -16263,6 +16317,11 @@
       <c r="P358" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q358" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -16367,26 +16426,41 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E360" t="inlineStr"/>
       <c r="F360" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="G360" t="inlineStr"/>
-      <c r="H360" t="inlineStr"/>
-      <c r="I360" t="inlineStr"/>
-      <c r="J360" t="inlineStr"/>
-      <c r="K360" t="inlineStr"/>
-      <c r="L360" t="inlineStr"/>
-      <c r="M360" t="inlineStr"/>
       <c r="N360" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="O360" t="inlineStr"/>
-      <c r="P360" t="inlineStr"/>
+      <c r="Q360" t="inlineStr">
+        <is>
+          <r>
+            <t>F26V</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>NA</t>
+          </r>
+          <r>
+            <t xml:space="preserve">, </t>
+          </r>
+          <r>
+            <t>A62T</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>24</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="361"/>
     <row r="362">
@@ -16446,6 +16520,11 @@
       <c r="P362" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q362" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -16550,18 +16629,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E364" t="inlineStr"/>
-      <c r="F364" t="inlineStr"/>
-      <c r="G364" t="inlineStr"/>
-      <c r="H364" t="inlineStr"/>
-      <c r="I364" t="inlineStr"/>
-      <c r="J364" t="inlineStr"/>
-      <c r="K364" t="inlineStr"/>
-      <c r="L364" t="inlineStr"/>
-      <c r="M364" t="inlineStr"/>
-      <c r="N364" t="inlineStr"/>
-      <c r="O364" t="inlineStr"/>
-      <c r="P364" t="inlineStr"/>
     </row>
     <row r="365"/>
     <row r="366">
@@ -16621,6 +16688,11 @@
       <c r="P366" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q366" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -16725,18 +16797,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E368" t="inlineStr"/>
-      <c r="F368" t="inlineStr"/>
-      <c r="G368" t="inlineStr"/>
-      <c r="H368" t="inlineStr"/>
-      <c r="I368" t="inlineStr"/>
-      <c r="J368" t="inlineStr"/>
-      <c r="K368" t="inlineStr"/>
-      <c r="L368" t="inlineStr"/>
-      <c r="M368" t="inlineStr"/>
-      <c r="N368" t="inlineStr"/>
-      <c r="O368" t="inlineStr"/>
-      <c r="P368" t="inlineStr"/>
     </row>
     <row r="369"/>
     <row r="370">
@@ -16796,6 +16856,11 @@
       <c r="P370" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q370" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -16900,18 +16965,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E372" t="inlineStr"/>
-      <c r="F372" t="inlineStr"/>
-      <c r="G372" t="inlineStr"/>
-      <c r="H372" t="inlineStr"/>
-      <c r="I372" t="inlineStr"/>
-      <c r="J372" t="inlineStr"/>
-      <c r="K372" t="inlineStr"/>
-      <c r="L372" t="inlineStr"/>
-      <c r="M372" t="inlineStr"/>
-      <c r="N372" t="inlineStr"/>
-      <c r="O372" t="inlineStr"/>
-      <c r="P372" t="inlineStr"/>
     </row>
     <row r="373"/>
     <row r="374">
@@ -16971,6 +17024,11 @@
       <c r="P374" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q374" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -17075,22 +17133,24 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E376" t="inlineStr"/>
-      <c r="F376" t="inlineStr"/>
-      <c r="G376" t="inlineStr"/>
-      <c r="H376" t="inlineStr"/>
       <c r="I376" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J376" t="inlineStr"/>
-      <c r="K376" t="inlineStr"/>
-      <c r="L376" t="inlineStr"/>
-      <c r="M376" t="inlineStr"/>
-      <c r="N376" t="inlineStr"/>
-      <c r="O376" t="inlineStr"/>
-      <c r="P376" t="inlineStr"/>
+      <c r="Q376" t="inlineStr">
+        <is>
+          <r>
+            <t>S30L</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>67</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="377"/>
     <row r="378">
@@ -17150,6 +17210,11 @@
       <c r="P378" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="Q378" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -17254,26 +17319,41 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E380" t="inlineStr"/>
       <c r="F380" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="G380" t="inlineStr"/>
-      <c r="H380" t="inlineStr"/>
-      <c r="I380" t="inlineStr"/>
-      <c r="J380" t="inlineStr"/>
-      <c r="K380" t="inlineStr"/>
-      <c r="L380" t="inlineStr"/>
-      <c r="M380" t="inlineStr"/>
       <c r="N380" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="O380" t="inlineStr"/>
-      <c r="P380" t="inlineStr"/>
+      <c r="Q380" t="inlineStr">
+        <is>
+          <r>
+            <t>R26K</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>40</t>
+          </r>
+          <r>
+            <t xml:space="preserve">, </t>
+          </r>
+          <r>
+            <t>V62I</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>40</t>
+          </r>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Reference_seqs/HCV_Subtype_Ref_vs_Comet_Subtype_Consensus_Aligned_NS5A_NTD.xlsx
+++ b/Reference_seqs/HCV_Subtype_Ref_vs_Comet_Subtype_Consensus_Aligned_NS5A_NTD.xlsx
@@ -1859,6 +1859,11 @@
           <t>R</t>
         </is>
       </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="M32" t="inlineStr">
         <is>
           <t>P</t>
@@ -1879,13 +1884,25 @@
             <t xml:space="preserve">, </t>
           </r>
           <r>
+            <t>M31L</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>50</t>
+          </r>
+          <r>
+            <t xml:space="preserve">, </t>
+          </r>
+          <r>
             <t>S58P</t>
           </r>
           <r>
             <rPr>
               <vertAlign val="subscript"/>
             </rPr>
-            <t>86</t>
+            <t>88</t>
           </r>
         </is>
       </c>
@@ -2055,24 +2072,6 @@
       <c r="D36" t="inlineStr">
         <is>
           <t>Consensus</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <r>
-            <t>L31M</t>
-          </r>
-          <r>
-            <rPr>
-              <vertAlign val="subscript"/>
-            </rPr>
-            <t>57</t>
-          </r>
         </is>
       </c>
     </row>
@@ -3690,7 +3689,7 @@
             <rPr>
               <vertAlign val="subscript"/>
             </rPr>
-            <t>100</t>
+            <t>99</t>
           </r>
         </is>
       </c>
@@ -6538,7 +6537,7 @@
             <rPr>
               <vertAlign val="subscript"/>
             </rPr>
-            <t>86</t>
+            <t>88</t>
           </r>
         </is>
       </c>
@@ -6724,7 +6723,7 @@
             <rPr>
               <vertAlign val="subscript"/>
             </rPr>
-            <t>57</t>
+            <t>67</t>
           </r>
         </is>
       </c>
@@ -7773,7 +7772,7 @@
             <rPr>
               <vertAlign val="subscript"/>
             </rPr>
-            <t>93</t>
+            <t>88</t>
           </r>
           <r>
             <t xml:space="preserve">, </t>
@@ -7785,7 +7784,7 @@
             <rPr>
               <vertAlign val="subscript"/>
             </rPr>
-            <t>84</t>
+            <t>89</t>
           </r>
         </is>
       </c>
@@ -10062,6 +10061,24 @@
           <t>Consensus</t>
         </is>
       </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="Q216" t="inlineStr">
+        <is>
+          <r>
+            <t>R38K</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>NA</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="217"/>
     <row r="218">
@@ -10970,7 +10987,7 @@
             <rPr>
               <vertAlign val="subscript"/>
             </rPr>
-            <t>88</t>
+            <t>80</t>
           </r>
         </is>
       </c>
@@ -11828,7 +11845,7 @@
             <rPr>
               <vertAlign val="subscript"/>
             </rPr>
-            <t>71</t>
+            <t>70</t>
           </r>
         </is>
       </c>
@@ -12014,7 +12031,7 @@
             <rPr>
               <vertAlign val="subscript"/>
             </rPr>
-            <t>71</t>
+            <t>70</t>
           </r>
         </is>
       </c>
@@ -12722,7 +12739,7 @@
             <rPr>
               <vertAlign val="subscript"/>
             </rPr>
-            <t>35</t>
+            <t>38</t>
           </r>
         </is>
       </c>
@@ -15869,183 +15886,15 @@
           <t>Consensus</t>
         </is>
       </c>
-    </row>
-    <row r="349"/>
-    <row r="350">
-      <c r="A350" s="1" t="inlineStr">
-        <is>
-          <t>Gene</t>
-        </is>
-      </c>
-      <c r="B350" s="1" t="inlineStr">
-        <is>
-          <t>Genotype</t>
-        </is>
-      </c>
-      <c r="C350" s="1" t="inlineStr">
-        <is>
-          <t>Subtype</t>
-        </is>
-      </c>
-      <c r="D350" s="1" t="inlineStr">
-        <is>
-          <t>Sequence</t>
-        </is>
-      </c>
-      <c r="E350" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="F350" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="G350" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="H350" s="1" t="n">
-        <v>29</v>
-      </c>
-      <c r="I350" s="1" t="n">
-        <v>30</v>
-      </c>
-      <c r="J350" s="1" t="n">
-        <v>31</v>
-      </c>
-      <c r="K350" s="1" t="n">
-        <v>32</v>
-      </c>
-      <c r="L350" s="1" t="n">
-        <v>38</v>
-      </c>
-      <c r="M350" s="1" t="n">
-        <v>58</v>
-      </c>
-      <c r="N350" s="1" t="n">
-        <v>62</v>
-      </c>
-      <c r="O350" s="1" t="n">
-        <v>92</v>
-      </c>
-      <c r="P350" s="1" t="n">
-        <v>93</v>
-      </c>
-      <c r="Q350" s="1" t="inlineStr">
-        <is>
-          <t>Mutations</t>
-        </is>
-      </c>
-    </row>
-    <row r="351">
-      <c r="A351" t="inlineStr">
-        <is>
-          <t>NS5A_NTD</t>
-        </is>
-      </c>
-      <c r="B351" t="inlineStr">
-        <is>
-          <t>GT6</t>
-        </is>
-      </c>
-      <c r="C351" t="inlineStr">
-        <is>
-          <t>6v</t>
-        </is>
-      </c>
-      <c r="D351" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="E351" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F351" t="inlineStr">
+      <c r="K348" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="G351" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="H351" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I351" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="J351" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="K351" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="L351" t="inlineStr">
-        <is>
-          <t>Q</t>
-        </is>
-      </c>
-      <c r="M351" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="N351" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="O351" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="P351" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-    </row>
-    <row r="352">
-      <c r="A352" t="inlineStr">
-        <is>
-          <t>NS5A_NTD</t>
-        </is>
-      </c>
-      <c r="B352" t="inlineStr">
-        <is>
-          <t>GT6</t>
-        </is>
-      </c>
-      <c r="C352" t="inlineStr">
-        <is>
-          <t>6v</t>
-        </is>
-      </c>
-      <c r="D352" t="inlineStr">
-        <is>
-          <t>Consensus</t>
-        </is>
-      </c>
-      <c r="K352" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="Q352" t="inlineStr">
+      <c r="Q348" t="inlineStr">
         <is>
           <r>
-            <t>V32I</t>
+            <t>I32V</t>
           </r>
           <r>
             <rPr>
@@ -16053,6 +15902,174 @@
             </rPr>
             <t>NA</t>
           </r>
+        </is>
+      </c>
+    </row>
+    <row r="349"/>
+    <row r="350">
+      <c r="A350" s="1" t="inlineStr">
+        <is>
+          <t>Gene</t>
+        </is>
+      </c>
+      <c r="B350" s="1" t="inlineStr">
+        <is>
+          <t>Genotype</t>
+        </is>
+      </c>
+      <c r="C350" s="1" t="inlineStr">
+        <is>
+          <t>Subtype</t>
+        </is>
+      </c>
+      <c r="D350" s="1" t="inlineStr">
+        <is>
+          <t>Sequence</t>
+        </is>
+      </c>
+      <c r="E350" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="F350" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="G350" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="H350" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="I350" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="J350" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="K350" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="L350" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="M350" s="1" t="n">
+        <v>58</v>
+      </c>
+      <c r="N350" s="1" t="n">
+        <v>62</v>
+      </c>
+      <c r="O350" s="1" t="n">
+        <v>92</v>
+      </c>
+      <c r="P350" s="1" t="n">
+        <v>93</v>
+      </c>
+      <c r="Q350" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>NS5A_NTD</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>GT6</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>6v</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M351" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="N351" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="O351" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="P351" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>NS5A_NTD</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>GT6</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>6v</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>Consensus</t>
         </is>
       </c>
     </row>
@@ -16965,6 +16982,24 @@
           <t>Consensus</t>
         </is>
       </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Q372" t="inlineStr">
+        <is>
+          <r>
+            <t>S30C</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>50</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="373"/>
     <row r="374">
@@ -17147,7 +17182,7 @@
             <rPr>
               <vertAlign val="subscript"/>
             </rPr>
-            <t>67</t>
+            <t>100</t>
           </r>
         </is>
       </c>
